--- a/haver/haver-api_PCA/tickerlist_confirmed.xlsx
+++ b/haver/haver-api_PCA/tickerlist_confirmed.xlsx
@@ -2719,7 +2719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2899,48 +2899,48 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>capex</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Producer Shipments: Capital Goods (SA, 2020=100)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>JPSIISCT@JAPAN</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1978-01</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>자본재 출하 총계 — capex 장기이력 확보용(기존 BO/GM은 2018~)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>CONSUMER</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>consumer</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Wholesale and Retail Sales: Total (Bil.Yen)</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>WRS@JAPAN</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>1970-01</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>명목이지만 속보성 유지(CAI 1개월 랙)</t>
-        </is>
-      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -2950,17 +2950,17 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Consumption Activity Index [Real] (SA)</t>
+          <t>Wholesale and Retail Sales: Total (Bil.Yen)</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>JPSCAIC@JAPAN</t>
+          <t>WRS@JAPAN</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>2003-01</t>
+          <t>1970-01</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>명목 CAI 제외</t>
+          <t>명목이지만 속보성 유지(CAI 1개월 랙)</t>
         </is>
       </c>
     </row>
@@ -2982,17 +2982,17 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Consumer Conf: Overall Livelihood (SA)</t>
+          <t>Consumption Activity Index [Real] (SA)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>S158VCIS@INTSRVYS</t>
+          <t>JPSCAIC@JAPAN</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>1982-06</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>종합(VCIT)은 중복 택1 제외</t>
+          <t>명목 CAI 제외</t>
         </is>
       </c>
     </row>
@@ -3014,73 +3014,73 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
+          <t>Consumer Conf: Overall Livelihood (SA)</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>S158VCIS@INTSRVYS</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>1982-06</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>종합(VCIT)은 중복 택1 제외</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>consumer</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
           <t>EW DI Current Conditions: Retail Sales (SA)</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>S158VBIR@INTSRVYS</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>2002-01</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>가계(VBIH)는 중복 택1 제외</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>EXPORT</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>export</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Export Shipments: Investment Goods (SA)</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>JPSHX202@JAPAN</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>1998-01</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>Capital Goods(203)·Final Demand(201) 중복 제외</t>
-        </is>
-      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -3090,17 +3090,17 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Real Exports (SA, 2020=100) [BOJ]</t>
+          <t>Export Shipments: Investment Goods (SA)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>JPSIVX@JAPAN</t>
+          <t>JPSHX202@JAPAN</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>1975-01</t>
+          <t>1998-01</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>MoF 명목(VEATTL2) 제외</t>
+          <t>Capital Goods(203)·Final Demand(201) 중복 제외</t>
         </is>
       </c>
     </row>
@@ -3122,113 +3122,117 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
+          <t>Real Exports (SA, 2020=100) [BOJ]</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>JPSIVX@JAPAN</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>1975-01</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>MoF 명목(VEATTL2) 제외</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>export</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
           <t>Export Shipments: Consumer Durables (SA)</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>JPSHX224@JAPAN</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>1998-01</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>Consumer Goods(223) 중복 제외</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>HOUSING (신설)</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>housing</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>Housing Starts: New Construction (SA, Thous Units)</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>COSTN2@JAPAN</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>1965-01</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>JP housing 지표가 이것뿐이라 카테고리 미성립(2개 미만) — 사용자 결정으로 제외</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>LABOR</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>labor</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Rate of Filled Vacancies (SA)</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>JAFVRN2@JAPAN</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>1963-01</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -3238,12 +3242,12 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Ratio of Active Job Openings to Applications (SA)</t>
+          <t>Rate of Filled Vacancies (SA)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>JAOR2@JAPAN</t>
+          <t>JAFVRN2@JAPAN</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -3266,17 +3270,17 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Unemployment Rate (SA)</t>
+          <t>Ratio of Active Job Openings to Applications (SA)</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>S158ELUR@G10</t>
+          <t>JAOR2@JAPAN</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>1953-01</t>
+          <t>1963-01</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -3284,11 +3288,7 @@
           <t>확정</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>실업자수(FLUED2)는 중복 제외</t>
-        </is>
-      </c>
+      <c r="F21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>LFS: Total Employed (SA)</t>
+          <t>Unemployment Rate (SA)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>FLED2@JAPAN</t>
+          <t>S158ELUR@G10</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -3316,7 +3316,11 @@
           <t>확정</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr"/>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>실업자수(FLUED2)는 중복 제외</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -3326,17 +3330,17 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Total Hours Worked: All Surveyed Inds (NSA)</t>
+          <t>LFS: Total Employed (SA)</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>MHFA@JAPAN</t>
+          <t>FLED2@JAPAN</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>1990-01</t>
+          <t>1953-01</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -3354,97 +3358,97 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
+          <t>Total Hours Worked: All Surveyed Inds (NSA)</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>MHFA@JAPAN</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>1990-01</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>labor</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
           <t>EW DI Current Conditions: Employment (SA)</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>S158VBIE@INTSRVYS</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>2002-01</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>labor</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>Common Establishments LFS: All Industry: Regular Pay (Yen)</t>
         </is>
       </c>
-      <c r="C25" s="10" t="inlineStr">
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>JPNECTT3@JAPAN</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="D26" s="10" t="inlineStr">
         <is>
           <t>2016-01</t>
         </is>
       </c>
-      <c r="E25" s="10" t="inlineStr">
+      <c r="E26" s="10" t="inlineStr">
         <is>
           <t>확정[wage]</t>
         </is>
       </c>
-      <c r="F25" s="11" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>현금급여총액(TT1)은 중복 택1 제외</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>LEI</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>LEI</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>EW DI Future Conditions [헤드라인] (SA)</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>S158VBET@INTSRVYS</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>2001-08</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr"/>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -3454,17 +3458,17 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>EW DI Future Conditions: Corporations (SA)</t>
+          <t>EW DI Future Conditions [헤드라인] (SA)</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>S158VBEC@INTSRVYS</t>
+          <t>S158VBET@INTSRVYS</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>2002-01</t>
+          <t>2001-08</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -3482,12 +3486,12 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>EW DI Future Conditions: Retail Sales (SA)</t>
+          <t>EW DI Future Conditions: Corporations (SA)</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>S158VBER@INTSRVYS</t>
+          <t>S158VBEC@INTSRVYS</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -3500,11 +3504,7 @@
           <t>확정</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>consumer에서 이동</t>
-        </is>
-      </c>
+      <c r="F29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>EW DI Future Conditions: Households (SA)</t>
+          <t>EW DI Future Conditions: Retail Sales (SA)</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>S158VBEH@INTSRVYS</t>
+          <t>S158VBER@INTSRVYS</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -3546,27 +3546,27 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>TDB Economic Trends: Total: 3 Month Later (DI)</t>
+          <t>EW DI Future Conditions: Households (SA)</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>N158VRO@INTSRVYS</t>
+          <t>S158VBEH@INTSRVYS</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>2004-04</t>
+          <t>2002-01</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>확정</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>TDB Economic Trends 2020-08 단종 — JP lei 최근 6년치 소실</t>
+          <t>consumer에서 이동</t>
         </is>
       </c>
     </row>
@@ -3578,25 +3578,29 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>EW DI Current Conditions [헤드라인] (SA)</t>
+          <t>TDB Economic Trends: Total: 3 Month Later (DI)</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>S158VBIT@INTSRVYS</t>
+          <t>N158VRO@INTSRVYS</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>2001-08</t>
+          <t>2004-04</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr"/>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>TDB Economic Trends 2020-08 단종 — JP lei 최근 6년치 소실</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -3606,17 +3610,17 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>EW DI Current Conditions: Corporations (SA)</t>
+          <t>EW DI Current Conditions [헤드라인] (SA)</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>S158VBIC@INTSRVYS</t>
+          <t>S158VBIT@INTSRVYS</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>2002-01</t>
+          <t>2001-08</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -3634,57 +3638,85 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
+          <t>EW DI Current Conditions: Corporations (SA)</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>S158VBIC@INTSRVYS</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>2002-01</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>LEI</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
           <t>Composite Index: Leading Index [내각부]</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>JPNCILD@JAPAN</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>1985-01</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>선행DI(DILD)는 중복 택1 제외</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>LEI</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>Composite Index: Coincident Index [내각부]</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D35" s="8" t="inlineStr">
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
-      <c r="F35" s="9" t="inlineStr">
+      <c r="F36" s="9" t="inlineStr">
         <is>
           <t>동행지수</t>
         </is>
@@ -3701,7 +3733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3909,108 +3941,112 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>capex</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Exports: Capital Goods (SA, Mil.Pounds)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>S112IXK@G10</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1997-01</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>자본재 수출은 해외수요 — capex보다 export 성격. ENGW(수입)로 교체</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>capex</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Imports of Capital Goods [실질] (SA, Mil.Chn.2023.GBP)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ENGW@UK</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1997-01</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>국내 설비투자 수요 대리 — capex 장기이력 확보</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>capex</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BoE Agents' Survey: Construction Output (NSA, %Bal)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>UNVAO3@UK</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1997-07</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>기존 BoE Agents(UNVAI3/UNVAA3, 2017-10~)의 장기 계열</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>CONSUMER</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>consumer</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>UK PMI: Services Business Activity [Latest incl Flash] (SA)</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>M112VPMS@INTSRVYS</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>2021-01</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>2021-01 시작 — consumer 기간 단축 감수하고 채택</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>consumer</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>GB Retail Sales Volume incl Auto Fuel (SA)</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>J5EK@UK</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>1996-01</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>ex-fuel(J467) 택1 제외, value 명목 제외</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>consumer</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Dist Trades: Retail: Stocks to Expected Sales (%Bal)</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>UCBRSS@UK</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>1983-08</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -4020,17 +4056,17 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>GfK: General Economic Situation Last 12M (NSA)</t>
+          <t>UK PMI: Services Business Activity [Latest incl Flash] (SA)</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>UGFCGL@UK</t>
+          <t>M112VPMS@INTSRVYS</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>1996-01</t>
+          <t>2021-01</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -4038,7 +4074,11 @@
           <t>확정</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr"/>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>2021-01 시작 — consumer 기간 단축 감수하고 채택</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -4048,12 +4088,12 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>GfK: Major Purchases at Present (NSA)</t>
+          <t>GB Retail Sales Volume incl Auto Fuel (SA)</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>UGFCM@UK</t>
+          <t>J5EK@UK</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -4068,7 +4108,7 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>종합 바로미터(UGFCI)는 세부와 중복 제외</t>
+          <t>ex-fuel(J467) 택1 제외, value 명목 제외</t>
         </is>
       </c>
     </row>
@@ -4080,17 +4120,17 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Dist Trades: Wholesale Vol of Sales YoY (%Bal)</t>
+          <t>Dist Trades: Retail: Stocks to Expected Sales (%Bal)</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>UCBWSA@UK</t>
+          <t>UCBRSS@UK</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>1983-07</t>
+          <t>1983-08</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -4108,17 +4148,17 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Consumer Credit ex Student: Gross Lending (SA)</t>
+          <t>GfK: General Economic Situation Last 12M (NSA)</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>USB3PU@UK</t>
+          <t>UGFCGL@UK</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>1993-04</t>
+          <t>1996-01</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -4136,17 +4176,17 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>New Car Registrations: Private (NSA)</t>
+          <t>GfK: Major Purchases at Present (NSA)</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>UNCREGP@UK</t>
+          <t>UGFCM@UK</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>2001-01</t>
+          <t>1996-01</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -4154,39 +4194,59 @@
           <t>확정</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr"/>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>종합 바로미터(UGFCI)는 세부와 중복 제외</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>HOUSING</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>consumer</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Dist Trades: Wholesale Vol of Sales YoY (%Bal)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>UCBWSA@UK</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>1983-07</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>housing</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>RICS: Change in New Buyer Enquiries (SA)</t>
+          <t>Consumer Credit ex Student: Gross Lending (SA)</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>URSHQ@UK</t>
+          <t>USB3PU@UK</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>1999-04</t>
+          <t>1993-04</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -4199,22 +4259,22 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>housing</t>
+          <t>consumer</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>RICS: Change in Newly Agreed Sales (SA)</t>
+          <t>New Car Registrations: Private (NSA)</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>URSHG@UK</t>
+          <t>UNCREGP@UK</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>1999-04</t>
+          <t>2001-01</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -4222,39 +4282,19 @@
           <t>확정</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>Sales Avg 3Mo(URSHS)는 중복 제외</t>
-        </is>
-      </c>
+      <c r="F19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>housing</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>RICS: Stocks Avg/Chartered Surveyor (SA)</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>URSHV@UK</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>1978-01</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr"/>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>HOUSING</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -4264,17 +4304,17 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Residential Property Transactions (SA)</t>
+          <t>RICS: Change in New Buyer Enquiries (SA)</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>UKSPT@UK</t>
+          <t>URSHQ@UK</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>2005-04</t>
+          <t>1999-04</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -4292,17 +4332,17 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Mortgage Lending Total: Gross New Loans (SA)</t>
+          <t>RICS: Change in Newly Agreed Sales (SA)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>USVTVC@UK</t>
+          <t>URSHG@UK</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>1993-04</t>
+          <t>1999-04</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -4310,39 +4350,59 @@
           <t>확정</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr"/>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Sales Avg 3Mo(URSHS)는 중복 제외</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>EXPORT</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>housing</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>RICS: Stocks Avg/Chartered Surveyor (SA)</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>URSHV@UK</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>1978-01</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>export</t>
+          <t>housing</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>CBI Industrial Trends: Current Export Order Book (%Bal)</t>
+          <t>Residential Property Transactions (SA)</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>UCBIEO@UK</t>
+          <t>UKSPT@UK</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>1977-04</t>
+          <t>2005-04</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -4355,98 +4415,90 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
+          <t>housing</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Mortgage Lending Total: Gross New Loans (SA)</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>USVTVC@UK</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>1993-04</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>EXPORT</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
           <t>export</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Exports of Services (SA, 실질 Chn.2023)</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>IKBE@UK</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>1997-01</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>명목(IKBB) 대신 실질</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>export</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Trade Balance of Services (SA)</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>IKBG@UK</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>1997-01</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>±레벨 — 전처리 주의</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>LABOR (신설)</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>CBI Industrial Trends: Current Export Order Book (%Bal)</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>UCBIEO@UK</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>1977-04</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>labor</t>
+          <t>export</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Unemployment Rate: 16+ [3-Mo MA] (SA, %)</t>
+          <t>Exports of Services (SA, 실질 Chn.2023)</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>S112ELUR@G10</t>
+          <t>IKBE@UK</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>1971-02</t>
+          <t>1997-01</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -4456,229 +4508,213 @@
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>LFS 3개월 이동평균 방식</t>
+          <t>명목(IKBB) 대신 실질</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
+          <t>export</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Trade Balance of Services (SA)</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>IKBG@UK</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>1997-01</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>±레벨 — 전처리 주의</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>LABOR (신설)</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
           <t>labor</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Unemployment Rate: 16+ [3-Mo MA] (SA, %)</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>S112ELUR@G10</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>1971-02</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>LFS 3개월 이동평균 방식</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>labor</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>LFS Employment: 16+ [3-Mo MA] (SA, Thous)</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>S112ELE@G10</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>1971-02</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>labor</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Job Vacancies ex Agriculture (SA, Thous)</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>AP2Y@UK</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>2001-05</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>labor</t>
-        </is>
-      </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>Average Weekly Earnings: Whole Economy (NSA, GBP)</t>
-        </is>
-      </c>
-      <c r="C31" s="10" t="inlineStr">
-        <is>
-          <t>KA46@UK</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>2000-01</t>
-        </is>
-      </c>
-      <c r="E31" s="10" t="inlineStr">
-        <is>
-          <t>확정[wage]</t>
-        </is>
-      </c>
-      <c r="F31" s="11" t="inlineStr">
-        <is>
-          <t>HMRC 페이롤·REC 서베이는 Haver에 없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>LEI</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="n"/>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="n"/>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
+          <t>labor</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Job Vacancies ex Agriculture (SA, Thous)</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>AP2Y@UK</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>2001-05</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>labor</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>Average Weekly Earnings: Whole Economy (NSA, GBP)</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>KA46@UK</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>2000-01</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>확정[wage]</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>HMRC 페이롤·REC 서베이는 Haver에 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
           <t>LEI</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B35" s="5" t="n"/>
+      <c r="C35" s="5" t="n"/>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>LEI</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>CBI: Volume of Output Over Next 3 Months (%Bal)</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>UCBIVO@UK</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>1975-02</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>LEI</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>CBI: Current Total Order Book (%Bal)</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>UCBITO@UK</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>1977-04</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>LEI</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Lloyds Business Barometer: Activity Next 12M (%Bal)</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>N112OL1T@INTSRVYS</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2002-01</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>CBI 편중 완화 — 별도 소스 선행지표</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>LEI</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>GfK Consumer Confidence Barometer [헤드라인] (%Bal)</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>N112VGI@INTSRVYS</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>1974-01</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>consumer의 UGFCGL·UGFCM 상위 합성 — 중복 감안 채택</t>
-        </is>
-      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -4688,57 +4724,149 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
+          <t>CBI: Current Total Order Book (%Bal)</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>UCBITO@UK</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>1977-04</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>LEI</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Lloyds Business Barometer: Activity Next 12M (%Bal)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>N112OL1T@INTSRVYS</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2002-01</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>CBI 편중 완화 — 별도 소스 선행지표</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>LEI</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>GfK Consumer Confidence Barometer [헤드라인] (%Bal)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>N112VGI@INTSRVYS</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1974-01</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>consumer의 UGFCGL·UGFCM 상위 합성 — 중복 감안 채택</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>LEI</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
           <t>UK PMI: Manufacturing Output [Latest incl Flash] (SA)</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>M112VPMG@INTSRVYS</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>2021-01</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
         <is>
           <t>2021-01 시작 — lei 기간 단축 감수하고 채택</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>LEI</t>
         </is>
       </c>
-      <c r="B38" s="9" t="inlineStr">
+      <c r="B41" s="9" t="inlineStr">
         <is>
           <t>Unemployment: Claimant Count Rate (SA)</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>BCJE@UK</t>
         </is>
       </c>
-      <c r="D38" s="8" t="inlineStr">
+      <c r="D41" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr">
+      <c r="E41" s="8" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
-      <c r="F38" s="9" t="inlineStr">
+      <c r="F41" s="9" t="inlineStr">
         <is>
           <t>사용자 삭제 확정</t>
         </is>

--- a/haver/haver-api_PCA/tickerlist_confirmed.xlsx
+++ b/haver/haver-api_PCA/tickerlist_confirmed.xlsx
@@ -6873,11 +6873,7 @@
       <c r="F19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>export</t>
-        </is>
-      </c>
+      <c r="A20" s="6" t="n"/>
       <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Export: Energy Products (SA) [파생용]</t>
@@ -6895,12 +6891,12 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>확정</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>사용자 결정으로 제외 (파생 미구현 + 총수출과 중복)</t>
+          <t>파생 계산 원료 — 비에너지수출(S156IX-V6911351) 계산용. 카테고리 비워 PCA에서는 제외됨</t>
         </is>
       </c>
     </row>
@@ -7236,27 +7232,27 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>US ISM Mfg: Employment / Imports [스필오버]</t>
+          <t>US ISM Mfg: Employment (SA) [스필오버]</t>
         </is>
       </c>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>NAPMEI/NAPMII@USECON</t>
+          <t>NAPMEI@USECON</t>
         </is>
       </c>
       <c r="D33" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1948-01</t>
         </is>
       </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>검증대기</t>
+          <t>확정</t>
         </is>
       </c>
       <c r="F33" s="15" t="inlineStr">
         <is>
-          <t>코드 추정 — fetch 시 확인</t>
+          <t>코드 검증 완료(1948-01~). NAPMII는 Imports가 아니라 Inventories였고 방향이 애매해 제외</t>
         </is>
       </c>
     </row>
